--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3C9B06-61C8-438E-BF6F-F7CF9DCE4C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F36424E7-ADE0-4876-8EEF-6E0D0E3FCD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{E5BF9A17-D330-4F6D-93EE-599B22DF2FC8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="My portfolio_2026-05-27" sheetId="1" r:id="rId1"/>
+    <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
   <si>
     <t>Symbol</t>
   </si>
@@ -101,13 +101,25 @@
   </si>
   <si>
     <t>Dividend</t>
+  </si>
+  <si>
+    <t>SET:BGRIM</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>SET:JMT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,315 +128,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri Light"/>
-      <family val="2"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -432,208 +150,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -656,44 +186,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -720,32 +250,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -772,24 +284,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -801,155 +295,176 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E89D979-C1E6-45B0-9E64-FE02752D2D3D}">
-  <dimension ref="A1:F26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,7 +504,7 @@
         <v>0.22</v>
       </c>
       <c r="F2" s="1">
-        <v>46128.583958333336</v>
+        <v>46128.583958333344</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1009,7 +524,7 @@
         <v>7.7</v>
       </c>
       <c r="F3" s="1">
-        <v>46090.083333333336</v>
+        <v>46090.083333333343</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1029,7 +544,7 @@
         <v>0.36</v>
       </c>
       <c r="F4" s="1">
-        <v>46087.083333333336</v>
+        <v>46087.083333333343</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1049,7 +564,7 @@
         <v>16.559999999999999</v>
       </c>
       <c r="F5" s="1">
-        <v>46070.083333333336</v>
+        <v>46070.083333333343</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,7 +604,7 @@
         <v>16.7</v>
       </c>
       <c r="F7" s="1">
-        <v>46065.083333333336</v>
+        <v>46065.083333333343</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1109,7 +624,7 @@
         <v>4.5</v>
       </c>
       <c r="F8" s="1">
-        <v>46064.401666666665</v>
+        <v>46064.401666666658</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1129,7 +644,7 @@
         <v>46.75</v>
       </c>
       <c r="F9" s="1">
-        <v>46064.401666666665</v>
+        <v>46064.401666666658</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1149,7 +664,7 @@
         <v>15.5</v>
       </c>
       <c r="F10" s="1">
-        <v>46062.083333333336</v>
+        <v>46062.083333333343</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1169,7 +684,7 @@
         <v>7.1</v>
       </c>
       <c r="F11" s="1">
-        <v>46062.083333333336</v>
+        <v>46062.083333333343</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,7 +704,7 @@
         <v>8.4</v>
       </c>
       <c r="F12" s="1">
-        <v>46062.083333333336</v>
+        <v>46062.083333333343</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1209,7 +724,7 @@
         <v>0.21</v>
       </c>
       <c r="F13" s="1">
-        <v>46059.604166666664</v>
+        <v>46059.604166666657</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1229,7 +744,7 @@
         <v>0.13</v>
       </c>
       <c r="F14" s="1">
-        <v>46059.604166666664</v>
+        <v>46059.604166666657</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1249,7 +764,7 @@
         <v>0.45</v>
       </c>
       <c r="F15" s="1">
-        <v>46058.604166666664</v>
+        <v>46058.604166666657</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1269,7 +784,7 @@
         <v>0.43</v>
       </c>
       <c r="F16" s="1">
-        <v>46052.604166666664</v>
+        <v>46052.604166666657</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1289,7 +804,7 @@
         <v>3.66</v>
       </c>
       <c r="F17" s="1">
-        <v>46052.083333333336</v>
+        <v>46052.083333333343</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1309,7 +824,7 @@
         <v>24</v>
       </c>
       <c r="F18" s="1">
-        <v>46052.083333333336</v>
+        <v>46052.083333333343</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,7 +844,7 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="F19" s="1">
-        <v>46049.083333333336</v>
+        <v>46049.083333333343</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,7 +864,7 @@
         <v>0.12</v>
       </c>
       <c r="F20" s="1">
-        <v>46048.604166666664</v>
+        <v>46048.604166666657</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1369,7 +884,7 @@
         <v>7.96</v>
       </c>
       <c r="F21" s="1">
-        <v>46048.083333333336</v>
+        <v>46048.083333333343</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1383,7 +898,7 @@
         <v>756</v>
       </c>
       <c r="F22" s="1">
-        <v>46162.403599537036</v>
+        <v>46162.403599537043</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1411,7 +926,7 @@
         <v>1010.4</v>
       </c>
       <c r="F24" s="1">
-        <v>46140.083333333336</v>
+        <v>46140.083333333343</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1425,7 +940,7 @@
         <v>86.4</v>
       </c>
       <c r="F25" s="1">
-        <v>46149.083333333336</v>
+        <v>46149.083333333343</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1442,7 +957,48 @@
         <v>46161.402499999997</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27">
+        <v>400</v>
+      </c>
+      <c r="D27">
+        <v>13.5</v>
+      </c>
+      <c r="E27">
+        <v>0.4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28">
+        <v>700</v>
+      </c>
+      <c r="D28">
+        <v>10.9</v>
+      </c>
+      <c r="E28">
+        <v>12.73</v>
+      </c>
+      <c r="F28" s="2">
+        <v>46167</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F36424E7-ADE0-4876-8EEF-6E0D0E3FCD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4D8D7D-5E7E-4F7E-BB20-57A32B5AAD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
   <si>
     <t>Symbol</t>
   </si>
@@ -110,6 +110,9 @@
   </si>
   <si>
     <t>SET:JMT</t>
+  </si>
+  <si>
+    <t>SET:AAV</t>
   </si>
 </sst>
 </file>
@@ -117,7 +120,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -156,7 +159,7 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -460,11 +463,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -997,6 +1001,26 @@
         <v>46167</v>
       </c>
     </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29">
+        <v>4500</v>
+      </c>
+      <c r="D29">
+        <v>1.08</v>
+      </c>
+      <c r="E29">
+        <v>8.16</v>
+      </c>
+      <c r="F29" s="2">
+        <v>46168</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4D8D7D-5E7E-4F7E-BB20-57A32B5AAD9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E932CBF-5C10-4E95-A2F6-21ED262AC2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="35">
   <si>
     <t>Symbol</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>SET:AAV</t>
+  </si>
+  <si>
+    <t>NASDAQ:MNDY</t>
+  </si>
+  <si>
+    <t>NASDAQ:WEN</t>
+  </si>
+  <si>
+    <t>NASDAQ:FIVN</t>
+  </si>
+  <si>
+    <t>NASDAQ:TRI</t>
   </si>
 </sst>
 </file>
@@ -463,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -593,39 +605,39 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7">
-        <v>7000</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>1.42</v>
+        <v>25.5</v>
       </c>
       <c r="E7">
-        <v>16.7</v>
+        <v>4.5</v>
       </c>
       <c r="F7" s="1">
-        <v>46065.083333333343</v>
+        <v>46064.401666666658</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="D8">
-        <v>25.5</v>
+        <v>34.75</v>
       </c>
       <c r="E8">
-        <v>4.5</v>
+        <v>46.75</v>
       </c>
       <c r="F8" s="1">
         <v>46064.401666666658</v>
@@ -633,39 +645,39 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="D9">
-        <v>34.75</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>46.75</v>
+        <v>15.5</v>
       </c>
       <c r="F9" s="1">
-        <v>46064.401666666658</v>
+        <v>46062.083333333343</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
       </c>
       <c r="C10">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D10">
-        <v>31</v>
+        <v>21.1</v>
       </c>
       <c r="E10">
-        <v>15.5</v>
+        <v>7.1</v>
       </c>
       <c r="F10" s="1">
         <v>46062.083333333343</v>
@@ -673,19 +685,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
       <c r="C11">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D11">
-        <v>21.1</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="E11">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="F11" s="1">
         <v>46062.083333333343</v>
@@ -693,39 +705,39 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
       </c>
       <c r="C12">
-        <v>300</v>
+        <v>5.8875400000000004</v>
       </c>
       <c r="D12">
-        <v>16.600000000000001</v>
+        <v>33.97</v>
       </c>
       <c r="E12">
-        <v>8.4</v>
+        <v>0.21</v>
       </c>
       <c r="F12" s="1">
-        <v>46062.083333333343</v>
+        <v>46059.604166666657</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
       </c>
       <c r="C13">
-        <v>5.8875400000000004</v>
+        <v>1</v>
       </c>
       <c r="D13">
-        <v>33.97</v>
+        <v>117.91</v>
       </c>
       <c r="E13">
-        <v>0.21</v>
+        <v>0.13</v>
       </c>
       <c r="F13" s="1">
         <v>46059.604166666657</v>
@@ -733,79 +745,79 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>3.2154340000000001</v>
       </c>
       <c r="D14">
-        <v>117.91</v>
+        <v>93.3</v>
       </c>
       <c r="E14">
-        <v>0.13</v>
+        <v>0.45</v>
       </c>
       <c r="F14" s="1">
-        <v>46059.604166666657</v>
+        <v>46058.604166666657</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
         <v>7</v>
       </c>
       <c r="C15">
-        <v>3.2154340000000001</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>93.3</v>
+        <v>39.700000000000003</v>
       </c>
       <c r="E15">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="F15" s="1">
-        <v>46058.604166666657</v>
+        <v>46052.604166666657</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
         <v>7</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="D16">
-        <v>39.700000000000003</v>
+        <v>2.1800000000000002</v>
       </c>
       <c r="E16">
-        <v>0.43</v>
+        <v>3.66</v>
       </c>
       <c r="F16" s="1">
-        <v>46052.604166666657</v>
+        <v>46052.083333333343</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="D17">
-        <v>2.1800000000000002</v>
+        <v>71.25</v>
       </c>
       <c r="E17">
-        <v>3.66</v>
+        <v>24</v>
       </c>
       <c r="F17" s="1">
         <v>46052.083333333343</v>
@@ -813,212 +825,272 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
       </c>
       <c r="C18">
-        <v>200</v>
+        <v>3200</v>
       </c>
       <c r="D18">
-        <v>71.25</v>
+        <v>0.88</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="F18" s="1">
-        <v>46052.083333333343</v>
+        <v>46049.083333333343</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
       </c>
       <c r="C19">
-        <v>3200</v>
+        <v>20</v>
       </c>
       <c r="D19">
-        <v>0.88</v>
+        <v>5.41</v>
       </c>
       <c r="E19">
-        <v>4.7300000000000004</v>
+        <v>0.12</v>
       </c>
       <c r="F19" s="1">
-        <v>46049.083333333343</v>
+        <v>46048.604166666657</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>1200</v>
       </c>
       <c r="D20">
-        <v>5.41</v>
+        <v>3.94</v>
       </c>
       <c r="E20">
-        <v>0.12</v>
+        <v>7.96</v>
       </c>
       <c r="F20" s="1">
-        <v>46048.604166666657</v>
+        <v>46048.083333333343</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="C21">
-        <v>1200</v>
-      </c>
-      <c r="D21">
-        <v>3.94</v>
-      </c>
-      <c r="E21">
-        <v>7.96</v>
+        <v>756</v>
       </c>
       <c r="F21" s="1">
-        <v>46048.083333333343</v>
+        <v>46162.403599537043</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>26</v>
       </c>
       <c r="C22">
-        <v>756</v>
+        <v>81</v>
       </c>
       <c r="F22" s="1">
-        <v>46162.403599537043</v>
+        <v>46162.401620370372</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
         <v>26</v>
       </c>
       <c r="C23">
-        <v>81</v>
+        <v>1010.4</v>
       </c>
       <c r="F23" s="1">
-        <v>46162.401620370372</v>
+        <v>46140.083333333343</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
         <v>26</v>
       </c>
       <c r="C24">
-        <v>1010.4</v>
+        <v>86.4</v>
       </c>
       <c r="F24" s="1">
-        <v>46140.083333333343</v>
+        <v>46149.083333333343</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25">
-        <v>86.4</v>
+        <v>591</v>
       </c>
       <c r="F25" s="1">
-        <v>46149.083333333343</v>
+        <v>46161.402499999997</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>591</v>
-      </c>
-      <c r="F26" s="1">
-        <v>46161.402499999997</v>
+        <v>400</v>
+      </c>
+      <c r="D26">
+        <v>13.5</v>
+      </c>
+      <c r="E26">
+        <v>0.4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
       </c>
       <c r="C27">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="D27">
-        <v>13.5</v>
+        <v>10.9</v>
       </c>
       <c r="E27">
-        <v>0.4</v>
-      </c>
-      <c r="F27" t="s">
-        <v>28</v>
+        <v>12.73</v>
+      </c>
+      <c r="F27" s="2">
+        <v>46167</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
       </c>
       <c r="C28">
-        <v>700</v>
+        <v>4500</v>
       </c>
       <c r="D28">
-        <v>10.9</v>
+        <v>1.08</v>
       </c>
       <c r="E28">
-        <v>12.73</v>
+        <v>8.16</v>
       </c>
       <c r="F28" s="2">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
         <v>7</v>
       </c>
       <c r="C29">
-        <v>4500</v>
+        <v>2.6</v>
       </c>
       <c r="D29">
-        <v>1.08</v>
+        <v>77.025000000000006</v>
       </c>
       <c r="E29">
-        <v>8.16</v>
+        <v>0.21</v>
       </c>
       <c r="F29" s="2">
+        <v>46065</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
+      </c>
+      <c r="D30">
+        <v>6.6398000000000001</v>
+      </c>
+      <c r="E30">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F30" s="2">
+        <v>46149</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>10</v>
+      </c>
+      <c r="D31">
+        <v>23.221</v>
+      </c>
+      <c r="E31">
+        <v>0.25</v>
+      </c>
+      <c r="F31" s="2">
         <v>46168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
+        <v>86.32</v>
+      </c>
+      <c r="E32">
+        <v>0.18</v>
+      </c>
+      <c r="F32" s="2">
+        <v>46171</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E932CBF-5C10-4E95-A2F6-21ED262AC2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4280CCC1-EFD2-40F0-B2C4-21892E7A7846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
   <si>
     <t>Symbol</t>
   </si>
@@ -125,6 +125,15 @@
   </si>
   <si>
     <t>NASDAQ:TRI</t>
+  </si>
+  <si>
+    <t>NASDAQ:SPCX</t>
+  </si>
+  <si>
+    <t>SET:AWC</t>
+  </si>
+  <si>
+    <t>SET:SISB</t>
   </si>
 </sst>
 </file>
@@ -475,7 +484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1093,6 +1102,86 @@
         <v>46171</v>
       </c>
     </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>163.59</v>
+      </c>
+      <c r="E33">
+        <v>0.17</v>
+      </c>
+      <c r="F33" s="2">
+        <v>46185</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34">
+        <v>0.92814399999999997</v>
+      </c>
+      <c r="D34">
+        <v>174.82</v>
+      </c>
+      <c r="E34">
+        <v>0.25</v>
+      </c>
+      <c r="F34" s="2">
+        <v>46188</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35">
+        <v>2000</v>
+      </c>
+      <c r="D35">
+        <v>2.44</v>
+      </c>
+      <c r="E35">
+        <v>0.36</v>
+      </c>
+      <c r="F35" s="2">
+        <v>46181</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36">
+        <v>600</v>
+      </c>
+      <c r="D36">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E36">
+        <v>9.7799999999999994</v>
+      </c>
+      <c r="F36" s="2">
+        <v>46182</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4280CCC1-EFD2-40F0-B2C4-21892E7A7846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3EE63-73EF-48DD-BCD9-8C703FD9EC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
   <si>
     <t>Symbol</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t>SET:SISB</t>
+  </si>
+  <si>
+    <t>NYSE:GIS</t>
   </si>
 </sst>
 </file>
@@ -484,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1182,6 +1185,26 @@
         <v>46182</v>
       </c>
     </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37">
+        <v>3</v>
+      </c>
+      <c r="D37">
+        <v>36.104999999999997</v>
+      </c>
+      <c r="E37">
+        <v>0.12</v>
+      </c>
+      <c r="F37" s="2">
+        <v>46199</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\script\portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3EE63-73EF-48DD-BCD9-8C703FD9EC52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455B6EEC-A91E-4D70-90FA-FAD8D6D94FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="42">
   <si>
     <t>Symbol</t>
   </si>
@@ -137,6 +137,15 @@
   </si>
   <si>
     <t>NYSE:GIS</t>
+  </si>
+  <si>
+    <t>NYSE:ACN</t>
+  </si>
+  <si>
+    <t>SET:BTG</t>
+  </si>
+  <si>
+    <t>SET:SNNP</t>
   </si>
 </sst>
 </file>
@@ -487,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -1205,6 +1214,66 @@
         <v>46199</v>
       </c>
     </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38">
+        <v>2.1829879999999999</v>
+      </c>
+      <c r="D38">
+        <v>137.55000000000001</v>
+      </c>
+      <c r="E38">
+        <v>0.48</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39">
+        <v>300</v>
+      </c>
+      <c r="D39">
+        <v>21.8</v>
+      </c>
+      <c r="E39">
+        <v>11</v>
+      </c>
+      <c r="F39" s="2">
+        <v>46209</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40">
+        <v>800</v>
+      </c>
+      <c r="D40">
+        <v>6.85</v>
+      </c>
+      <c r="E40">
+        <v>0.4</v>
+      </c>
+      <c r="F40" s="2">
+        <v>46204</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
